--- a/testakten/sozialrecht-pflegegrad-demenz-nachtwache-trier/kosten_nachtwache_und_umbau_2026.xlsx
+++ b/testakten/sozialrecht-pflegegrad-demenz-nachtwache-trier/kosten_nachtwache_und_umbau_2026.xlsx
@@ -7,9 +7,18 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Daten" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Angebote" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Finanzierung" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ereignisse" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
-  <definedNames/>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Angebote'!$A$1:$H$7</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="0">'Angebote'!$1:$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Finanzierung'!$A$1:$G$4</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="1">'Finanzierung'!$1:$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Ereignisse'!$A$1:$E$4</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="2">'Ereignisse'!$1:$1</definedName>
+  </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
@@ -17,7 +26,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="3">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -25,16 +34,31 @@
       <sz val="11"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="00183941"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <sz val="9"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E7EFF1"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -42,12 +66,23 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <bottom style="thin">
+        <color rgb="00C7D2D5"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -411,106 +446,622 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:D4"/>
+  <dimension ref="A1:H7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="33" customWidth="1" min="1" max="1"/>
-    <col width="26" customWidth="1" min="2" max="2"/>
-    <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="30" customWidth="1" min="4" max="4"/>
+    <col width="35" customWidth="1" min="1" max="1"/>
+    <col width="24" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="21" customWidth="1" min="6" max="6"/>
+    <col width="24" customWidth="1" min="7" max="7"/>
+    <col width="33" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Position</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>Anbieter</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>Betrag</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Angebotsdatum</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Netto EUR</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Brutto EUR</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Ausführung</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Kostenträger angefragt</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Nachtbereitschaft 20 Nächte</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>Porta Nigra GmbH</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>28.06.2026</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>4180.00</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>4180.00</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>01.07.-20.07.2026</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t>Pflegekasse</t>
+        </is>
+      </c>
+      <c r="H2" s="2" t="inlineStr">
+        <is>
+          <t>vorläufig privat</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>Herdabschaltung mit Zeitschaltung</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>Elektro Laux</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>24.06.2026</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>571.43</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>680.00</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>binnen 10 Tagen</t>
+        </is>
+      </c>
+      <c r="G3" s="2" t="inlineStr">
+        <is>
+          <t>Pflegekasse</t>
+        </is>
+      </c>
+      <c r="H3" s="2" t="inlineStr">
+        <is>
+          <t>Angebot offen</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>Türkontakt und Rufweiterleitung</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>SicherWohnen GmbH</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>26.06.2026</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>1000.00</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>1190.00</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>binnen 14 Tagen</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>Pflegekasse</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>Monatspauschale 24,90 EUR</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>Orientierungslicht Flur</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>Elektro Laux</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>24.06.2026</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>184.87</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>220.00</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>mit Herdabschaltung</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>Pflegekasse</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>nicht entschieden</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>Schwellenkeil Bad</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>Sanitätshaus Porta</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>30.06.2026</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>142.86</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>170.00</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>lagernd</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>Pflegekasse</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>Maßprüfung nötig</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>Teppichsicherung</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>Raumausstattung Zender</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>01.07.2026</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>226.89</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>270.00</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>eine Woche</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>privat</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>Vermieterzustimmung nicht nötig</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:H7"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup paperSize="9" fitToWidth="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:G4"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="17" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="30" customWidth="1" min="4" max="4"/>
+    <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="27" customWidth="1" min="6" max="6"/>
+    <col width="30" customWidth="1" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Monat</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Rente Anton EUR</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Pflegegeld EUR</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Eigenanteil Pflegedienst EUR</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Nachtwache EUR</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Tochter vorfinanziert EUR</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Bemerkung</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>Nachtwache 20 Nächte</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>Pflegedienst Porta Nigra</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>4180</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>nicht dauerhaft finanzierbar</t>
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>2026-05</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>1684.20</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>332.00</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>214.60</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>1820.00</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>1200.00</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t>erste Teilmonate</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>Herdabschaltung</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>Elektro Laux</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>680</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>Einbau binnen 10 Tagen</t>
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>1684.20</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>332.00</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>238.40</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>3190.00</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>2500.00</t>
+        </is>
+      </c>
+      <c r="G3" s="2" t="inlineStr">
+        <is>
+          <t>Ersparnisse Anton 690,00 EUR</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Türkontakt mit Rufweiterleitung</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>SicherWohnen GmbH</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>1190</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>Monatspauschale zusätzlich</t>
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>1684.20</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>332.00</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>offen</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>4180.00</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>offen</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>nur bis 20.07. beauftragt</t>
         </is>
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:G4"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup paperSize="9" fitToWidth="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:E4"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="30" customWidth="1" min="3" max="3"/>
+    <col width="13" customWidth="1" min="4" max="4"/>
+    <col width="22" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Datum</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Art</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Folgekosten</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Beleg</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Offen</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>Herdsituation</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>Topf 38,00 EUR</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>Foto</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>technische Sicherung</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>Sturz Bad</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>Fahrt Bereitschaft 22,00 EUR</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>Arztvermerk</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>Haltegriff</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-28</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>Sturz Teppich</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>keine Rechnung</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>Foto</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>Teppich sichern</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:E4"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup paperSize="9" fitToWidth="1"/>
 </worksheet>
 </file>